--- a/output/pdf_financials_xlsx/SVRS.xlsx
+++ b/output/pdf_financials_xlsx/SVRS.xlsx
@@ -4814,43 +4814,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.157378</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.157378</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.440274</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.440274</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.440274</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.369463</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.387453</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.318071</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.762151</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.732681</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.103</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.565</v>
       </c>
     </row>
     <row r="93">
@@ -9203,7 +9203,11 @@
           <t>Warrant reserves 16</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12379,7 +12383,11 @@
           <t>Warrant reserves (note 19)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -13163,7 +13171,11 @@
           <t>Warrant reserves (note 9)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -13931,7 +13943,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>2.157378</v>
       </c>
@@ -14962,7 +14978,11 @@
           <t>Warrant reserve 10 440,274</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -16163,7 +16183,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -36207,7 +36231,7 @@
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>0.038061</v>
+        <v>-0.038061</v>
       </c>
       <c r="L368" s="5" t="n">
         <v>-0.011127</v>

--- a/output/pdf_financials_xlsx/SVRS.xlsx
+++ b/output/pdf_financials_xlsx/SVRS.xlsx
@@ -861,13 +861,13 @@
         <v>2.963028</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9.420947</v>
+        <v>9.764557</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>12.096</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>18.026</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>-2.963028</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-9.420947</v>
+        <v>-9.764557</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-13.953</v>
@@ -2063,13 +2063,13 @@
         <v>0.070687</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.243745</v>
+        <v>0.070687</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.014571</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.043385</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.271551</v>
@@ -2155,13 +2155,13 @@
         <v>0.070687</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.717995</v>
+        <v>0.544937</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.044</v>
+        <v>1.058571</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4704</v>
+        <v>0.513785</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.439176</v>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -30088,13 +30088,13 @@
         </is>
       </c>
       <c r="O291" s="5" t="n">
-        <v>-9.764557</v>
+        <v>9.764557</v>
       </c>
       <c r="P291" s="5" t="n">
-        <v>-12.096</v>
+        <v>12.096</v>
       </c>
       <c r="Q291" s="5" t="n">
-        <v>-18.026</v>
+        <v>18.026</v>
       </c>
     </row>
     <row r="292">

--- a/output/pdf_financials_xlsx/SVRS.xlsx
+++ b/output/pdf_financials_xlsx/SVRS.xlsx
@@ -690,34 +690,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.011979</v>
+        <v>0.096979</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.012228</v>
+        <v>0.046228</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.012264</v>
+        <v>0.167764</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.011813</v>
+        <v>0.111813</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.012691</v>
+        <v>0.157691</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.157691</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.086879</v>
+        <v>1.396358</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.13806</v>
+        <v>1.669715</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.183715</v>
+        <v>1.02808</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.310612</v>
+        <v>2.006326</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.011979</v>
+        <v>0.096979</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.012228</v>
+        <v>0.046228</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.012264</v>
+        <v>0.167764</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.011813</v>
+        <v>0.111813</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.012691</v>
+        <v>0.157691</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.404474</v>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.011979</v>
+        <v>-0.096979</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.012228</v>
+        <v>-0.046228</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.012264</v>
+        <v>-0.167764</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.011813</v>
+        <v>-0.111813</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.012691</v>
+        <v>-0.157691</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.404474</v>
@@ -3506,13 +3506,13 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.266933</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.016</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>8.909000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3644,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.208777</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.858</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
     </row>
     <row r="68">
@@ -3782,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.363581</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="71">
@@ -3828,13 +3828,13 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.363581</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="72">
@@ -4012,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>4.29147</v>
+        <v>3.927889</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>4.861</v>
+        <v>4.549</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>12.5</v>
+        <v>12.312</v>
       </c>
     </row>
     <row r="76">
@@ -4162,13 +4162,13 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>1.369022</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="79">
@@ -4208,13 +4208,13 @@
         <v>0</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>1.369022</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="80">
@@ -4273,20 +4273,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.08957462929940416</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.06503889369057908</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01018758966350083</v>
       </c>
     </row>
     <row r="81">
@@ -4510,13 +4504,13 @@
         <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>9.044828000000001</v>
+        <v>7.675806</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>9.093</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>10.995</v>
+        <v>10.622</v>
       </c>
     </row>
     <row r="86">
@@ -5633,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.837653</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>1.241252</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -5845,19 +5839,19 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.107682</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.3584</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.233441</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.021401</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.093015</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -5866,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -8421,7 +8415,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -8660,7 +8658,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10269,7 +10271,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -10348,7 +10354,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -11832,7 +11842,11 @@
           <t>Lease obligations (note 16)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -11913,7 +11927,11 @@
           <t>Lease obligations (note 16)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -20744,7 +20762,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -22176,7 +22198,11 @@
           <t>Accretion 14,15,23</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -23547,7 +23573,11 @@
           <t>Accretion (notes 5, 16 and 17)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -26972,7 +27002,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -27371,7 +27405,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -33086,7 +33124,11 @@
           <t>Management, consulting fees and directors' fees (note 24)</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -34840,7 +34882,11 @@
           <t>Management, consulting fees and directors' fees (note 14)</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -36519,7 +36565,11 @@
           <t>Management, consulting and directors’ fees 14</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -38695,7 +38745,11 @@
           <t>Management, consulting and directors’ fees 15</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
